--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run1/epoch_120/per_file_predictions_epoch_120.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run1/epoch_120/per_file_predictions_epoch_120.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.5455,0.2837,0.0666,0.1306</t>
-  </si>
-  <si>
-    <t>0.0263,0.0034,0.0004,0.9899</t>
-  </si>
-  <si>
-    <t>0.7644,0.0149,0.0024,0.2444</t>
-  </si>
-  <si>
-    <t>0.0591,0.0089,0.0009,0.9798</t>
-  </si>
-  <si>
-    <t>0.9943,0.0054,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9950,0.0027,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9269,0.1441,0.0031,0.0009</t>
-  </si>
-  <si>
-    <t>0.9968,0.0014,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9902,0.0163,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9914,0.0062,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.9976,0.0022,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9950,0.0035,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.7756,0.0916,0.0738,0.0093</t>
-  </si>
-  <si>
-    <t>0.0559,0.0419,0.9296,0.0012</t>
-  </si>
-  <si>
-    <t>0.2103,0.0166,0.8955,0.0008</t>
-  </si>
-  <si>
-    <t>0.0452,0.0361,0.9042,0.0026</t>
-  </si>
-  <si>
-    <t>0.6290,0.0364,0.4637,0.0093</t>
-  </si>
-  <si>
-    <t>0.0085,0.9911,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.0400,0.9667,0.0036,0.0001</t>
-  </si>
-  <si>
-    <t>0.1749,0.8732,0.0075,0.0009</t>
-  </si>
-  <si>
-    <t>0.0652,0.9493,0.0032,0.0006</t>
-  </si>
-  <si>
-    <t>0.0072,0.9899,0.0030,0.0001</t>
-  </si>
-  <si>
-    <t>0.7613,0.0045,0.3685,0.0052</t>
-  </si>
-  <si>
-    <t>0.5621,0.0268,0.4826,0.0113</t>
-  </si>
-  <si>
-    <t>0.0187,0.0034,0.9813,0.0007</t>
-  </si>
-  <si>
-    <t>0.1550,0.0223,0.8362,0.0121</t>
-  </si>
-  <si>
-    <t>0.0498,0.0070,0.9619,0.0014</t>
-  </si>
-  <si>
-    <t>0.0876,0.0246,0.9109,0.0012</t>
-  </si>
-  <si>
-    <t>0.0047,0.0010,0.9944,0.0018</t>
-  </si>
-  <si>
-    <t>0.1055,0.9062,0.0118,0.0045</t>
-  </si>
-  <si>
-    <t>0.1877,0.6449,0.3249,0.0052</t>
-  </si>
-  <si>
-    <t>0.0007,0.0022,0.9966,0.0039</t>
-  </si>
-  <si>
-    <t>0.0209,0.5906,0.7069,0.0005</t>
-  </si>
-  <si>
-    <t>0.5730,0.3811,0.1330,0.0113</t>
-  </si>
-  <si>
-    <t>0.7182,0.2602,0.0473,0.0056</t>
-  </si>
-  <si>
-    <t>0.8983,0.1642,0.0063,0.0009</t>
-  </si>
-  <si>
-    <t>0.0693,0.8989,0.1060,0.0071</t>
-  </si>
-  <si>
-    <t>0.0123,0.6572,0.5562,0.0050</t>
-  </si>
-  <si>
-    <t>0.0055,0.0169,0.9819,0.0081</t>
-  </si>
-  <si>
-    <t>0.0146,0.2280,0.9235,0.0011</t>
-  </si>
-  <si>
-    <t>0.2027,0.0150,0.8039,0.0228</t>
-  </si>
-  <si>
-    <t>0.0105,0.0777,0.9594,0.0027</t>
-  </si>
-  <si>
-    <t>0.0292,0.8900,0.1073,0.0005</t>
-  </si>
-  <si>
-    <t>0.0033,0.0239,0.9901,0.0003</t>
-  </si>
-  <si>
-    <t>0.0633,0.5993,0.0143,0.7696</t>
-  </si>
-  <si>
-    <t>0.0015,0.9917,0.0025,0.0083</t>
-  </si>
-  <si>
-    <t>0.0022,0.9898,0.0309,0.0028</t>
-  </si>
-  <si>
-    <t>0.0005,0.9978,0.0044,0.0006</t>
-  </si>
-  <si>
-    <t>0.0040,0.0109,0.9871,0.0029</t>
-  </si>
-  <si>
-    <t>0.0104,0.1249,0.9616,0.0042</t>
-  </si>
-  <si>
-    <t>0.0189,0.0052,0.9803,0.0018</t>
-  </si>
-  <si>
-    <t>0.0063,0.0043,0.9939,0.0001</t>
-  </si>
-  <si>
-    <t>0.0710,0.0245,0.9224,0.0042</t>
-  </si>
-  <si>
-    <t>0.0021,0.0074,0.9931,0.0004</t>
-  </si>
-  <si>
-    <t>0.8904,0.1880,0.0063,0.0004</t>
-  </si>
-  <si>
-    <t>0.9751,0.0325,0.0036,0.0003</t>
-  </si>
-  <si>
-    <t>0.9828,0.0135,0.0043,0.0005</t>
-  </si>
-  <si>
-    <t>0.0214,0.0524,0.9476,0.0013</t>
-  </si>
-  <si>
-    <t>0.9751,0.0178,0.0051,0.0015</t>
-  </si>
-  <si>
-    <t>0.9933,0.0030,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9870,0.0155,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0053,0.9213,0.6536,0.0005</t>
-  </si>
-  <si>
-    <t>0.0143,0.0586,0.9536,0.0051</t>
-  </si>
-  <si>
-    <t>0.0181,0.1597,0.9165,0.0125</t>
-  </si>
-  <si>
-    <t>0.0012,0.6406,0.9798,0.0001</t>
-  </si>
-  <si>
-    <t>0.0142,0.0041,0.9833,0.0029</t>
-  </si>
-  <si>
-    <t>0.0282,0.9288,0.0324,0.0002</t>
-  </si>
-  <si>
-    <t>0.0293,0.9696,0.0054,0.0001</t>
-  </si>
-  <si>
-    <t>0.4818,0.0984,0.6207,0.0037</t>
-  </si>
-  <si>
-    <t>0.7508,0.0978,0.2480,0.0069</t>
-  </si>
-  <si>
-    <t>0.0067,0.0175,0.9778,0.0004</t>
-  </si>
-  <si>
-    <t>0.0011,0.9769,0.6715,0.0001</t>
-  </si>
-  <si>
-    <t>0.0027,0.8801,0.8372,0.0004</t>
-  </si>
-  <si>
-    <t>0.0015,0.9810,0.5735,0.0002</t>
-  </si>
-  <si>
-    <t>0.0017,0.9823,0.1982,0.0021</t>
-  </si>
-  <si>
-    <t>0.0155,0.0005,0.0157,0.9653</t>
-  </si>
-  <si>
-    <t>0.0108,0.0071,0.0007,0.9917</t>
-  </si>
-  <si>
-    <t>0.0450,0.0035,0.0024,0.9755</t>
-  </si>
-  <si>
-    <t>0.0241,0.0014,0.0084,0.9737</t>
-  </si>
-  <si>
-    <t>0.0265,0.0032,0.0023,0.9868</t>
-  </si>
-  <si>
-    <t>0.0105,0.0086,0.0192,0.9818</t>
-  </si>
-  <si>
-    <t>0.0011,0.9816,0.5700,0.0003</t>
-  </si>
-  <si>
-    <t>0.0015,0.8508,0.9413,0.0004</t>
-  </si>
-  <si>
-    <t>0.0096,0.8813,0.4848,0.0025</t>
-  </si>
-  <si>
-    <t>0.0050,0.3420,0.9618,0.0003</t>
-  </si>
-  <si>
-    <t>0.0034,0.9636,0.2657,0.0000</t>
-  </si>
-  <si>
-    <t>0.0248,0.6609,0.5083,0.0005</t>
-  </si>
-  <si>
-    <t>0.9949,0.0041,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9759,0.0349,0.0033,0.0005</t>
-  </si>
-  <si>
-    <t>0.9865,0.0134,0.0018,0.0002</t>
-  </si>
-  <si>
-    <t>0.9919,0.0091,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9942,0.0038,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9948,0.0036,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9796,0.0290,0.0006,0.0009</t>
-  </si>
-  <si>
-    <t>0.9908,0.0090,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9976,0.0006,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9956,0.0030,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9928,0.0088,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9984,0.0003,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9949,0.0009,0.0001,0.0012</t>
-  </si>
-  <si>
-    <t>0.9964,0.0028,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9966,0.0008,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9952,0.0045,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0081,0.0022,0.9906,0.0012</t>
-  </si>
-  <si>
-    <t>0.1757,0.0255,0.8728,0.0036</t>
-  </si>
-  <si>
-    <t>0.7565,0.0038,0.4611,0.0016</t>
-  </si>
-  <si>
-    <t>0.0100,0.0049,0.9886,0.0001</t>
-  </si>
-  <si>
-    <t>0.1393,0.8863,0.0169,0.0016</t>
-  </si>
-  <si>
-    <t>0.1562,0.8913,0.0061,0.0017</t>
-  </si>
-  <si>
-    <t>0.2406,0.8087,0.0035,0.0038</t>
-  </si>
-  <si>
-    <t>0.2149,0.8764,0.0016,0.0008</t>
-  </si>
-  <si>
-    <t>0.0358,0.9731,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.0266,0.9781,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.3635,0.7816,0.0011,0.0019</t>
-  </si>
-  <si>
-    <t>0.4423,0.4068,0.1613,0.0227</t>
-  </si>
-  <si>
-    <t>0.1623,0.0492,0.8119,0.0123</t>
-  </si>
-  <si>
-    <t>0.7011,0.0223,0.3280,0.0109</t>
-  </si>
-  <si>
-    <t>0.3952,0.0482,0.6255,0.0169</t>
-  </si>
-  <si>
-    <t>0.0163,0.3654,0.0114,0.9452</t>
-  </si>
-  <si>
-    <t>0.0105,0.9779,0.0189,0.0022</t>
-  </si>
-  <si>
-    <t>0.0003,0.9905,0.0019,0.0936</t>
-  </si>
-  <si>
-    <t>0.0700,0.9220,0.0110,0.0094</t>
-  </si>
-  <si>
-    <t>0.0008,0.9949,0.0678,0.0003</t>
-  </si>
-  <si>
-    <t>0.0322,0.9601,0.0576,0.0012</t>
-  </si>
-  <si>
-    <t>0.5862,0.5110,0.0306,0.0012</t>
-  </si>
-  <si>
-    <t>0.4289,0.6130,0.0559,0.0025</t>
-  </si>
-  <si>
-    <t>0.9732,0.0250,0.0052,0.0014</t>
-  </si>
-  <si>
-    <t>0.9449,0.0593,0.0022,0.0042</t>
-  </si>
-  <si>
-    <t>0.9894,0.0034,0.0009,0.0018</t>
-  </si>
-  <si>
-    <t>0.9694,0.0185,0.0096,0.0012</t>
-  </si>
-  <si>
-    <t>0.9926,0.0035,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9747,0.0207,0.0129,0.0013</t>
-  </si>
-  <si>
-    <t>0.9890,0.0031,0.0002,0.0012</t>
-  </si>
-  <si>
-    <t>0.9829,0.0104,0.0044,0.0006</t>
-  </si>
-  <si>
-    <t>0.0009,0.6458,0.9869,0.0001</t>
-  </si>
-  <si>
-    <t>0.0083,0.6142,0.8532,0.0009</t>
-  </si>
-  <si>
-    <t>0.0223,0.3366,0.8398,0.0060</t>
-  </si>
-  <si>
-    <t>0.0346,0.0150,0.9596,0.0002</t>
-  </si>
-  <si>
-    <t>0.8049,0.0559,0.0897,0.0334</t>
-  </si>
-  <si>
-    <t>0.7856,0.0338,0.2101,0.0040</t>
-  </si>
-  <si>
-    <t>0.2005,0.0204,0.8961,0.0003</t>
-  </si>
-  <si>
-    <t>0.6578,0.0371,0.3448,0.0281</t>
-  </si>
-  <si>
-    <t>0.0898,0.0072,0.0033,0.9590</t>
-  </si>
-  <si>
-    <t>0.0011,0.0014,0.0009,0.9981</t>
-  </si>
-  <si>
-    <t>0.0051,0.1296,0.0048,0.9866</t>
-  </si>
-  <si>
-    <t>0.0246,0.0010,0.0044,0.9859</t>
-  </si>
-  <si>
-    <t>0.0019,0.6423,0.9423,0.0004</t>
-  </si>
-  <si>
-    <t>0.9668,0.0304,0.0015,0.0017</t>
-  </si>
-  <si>
-    <t>0.0765,0.9290,0.0067,0.0032</t>
-  </si>
-  <si>
-    <t>0.9801,0.0154,0.0030,0.0010</t>
-  </si>
-  <si>
-    <t>0.6028,0.4106,0.0481,0.0011</t>
-  </si>
-  <si>
-    <t>0.9621,0.0280,0.0067,0.0024</t>
-  </si>
-  <si>
-    <t>0.5757,0.0152,0.0375,0.4319</t>
-  </si>
-  <si>
-    <t>0.9777,0.0134,0.0021,0.0022</t>
-  </si>
-  <si>
-    <t>0.0725,0.2965,0.7836,0.0309</t>
-  </si>
-  <si>
-    <t>0.9375,0.0007,0.0034,0.0549</t>
-  </si>
-  <si>
-    <t>0.8879,0.0156,0.0073,0.0752</t>
-  </si>
-  <si>
-    <t>0.1838,0.8287,0.0102,0.0119</t>
-  </si>
-  <si>
-    <t>0.9001,0.0423,0.0193,0.0136</t>
-  </si>
-  <si>
-    <t>0.7772,0.2353,0.0098,0.0129</t>
-  </si>
-  <si>
-    <t>0.4417,0.4446,0.1286,0.0079</t>
-  </si>
-  <si>
-    <t>0.8701,0.0584,0.0594,0.0020</t>
-  </si>
-  <si>
-    <t>0.7349,0.2360,0.0099,0.0131</t>
-  </si>
-  <si>
-    <t>0.9907,0.0088,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9832,0.0052,0.0002,0.0038</t>
-  </si>
-  <si>
-    <t>0.9925,0.0028,0.0013,0.0007</t>
-  </si>
-  <si>
-    <t>0.9818,0.0067,0.0048,0.0019</t>
-  </si>
-  <si>
-    <t>0.9672,0.0235,0.0071,0.0013</t>
-  </si>
-  <si>
-    <t>0.9822,0.0099,0.0032,0.0018</t>
-  </si>
-  <si>
-    <t>0.9904,0.0034,0.0002,0.0018</t>
-  </si>
-  <si>
-    <t>0.9900,0.0058,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.5750,0.6050,0.0054,0.0011</t>
-  </si>
-  <si>
-    <t>0.2966,0.7763,0.0121,0.0006</t>
-  </si>
-  <si>
-    <t>0.6928,0.4656,0.0038,0.0002</t>
-  </si>
-  <si>
-    <t>0.8484,0.0695,0.1331,0.0011</t>
-  </si>
-  <si>
-    <t>0.8183,0.3474,0.0021,0.0007</t>
-  </si>
-  <si>
-    <t>0.8863,0.1364,0.0185,0.0029</t>
-  </si>
-  <si>
-    <t>0.9566,0.0619,0.0040,0.0004</t>
-  </si>
-  <si>
-    <t>0.9434,0.0534,0.0003,0.0019</t>
-  </si>
-  <si>
-    <t>0.0018,0.0461,0.9944,0.0002</t>
-  </si>
-  <si>
-    <t>0.9843,0.0213,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.0040,0.0122,0.9907,0.0004</t>
-  </si>
-  <si>
-    <t>0.0110,0.0872,0.9597,0.0018</t>
-  </si>
-  <si>
-    <t>0.0253,0.0077,0.9737,0.0033</t>
-  </si>
-  <si>
-    <t>0.0088,0.0534,0.9692,0.0008</t>
-  </si>
-  <si>
-    <t>0.0173,0.0074,0.9825,0.0007</t>
-  </si>
-  <si>
-    <t>0.0121,0.0073,0.9808,0.0005</t>
-  </si>
-  <si>
-    <t>0.0022,0.0048,0.9946,0.0008</t>
-  </si>
-  <si>
-    <t>0.1601,0.2166,0.6040,0.0120</t>
-  </si>
-  <si>
-    <t>0.1715,0.0374,0.8572,0.0032</t>
-  </si>
-  <si>
-    <t>0.5888,0.0314,0.5032,0.0202</t>
-  </si>
-  <si>
-    <t>0.2574,0.4596,0.1875,0.0018</t>
-  </si>
-  <si>
-    <t>0.2898,0.2347,0.4650,0.0021</t>
-  </si>
-  <si>
-    <t>0.2481,0.0837,0.6704,0.0007</t>
-  </si>
-  <si>
-    <t>0.5301,0.0790,0.4626,0.0420</t>
-  </si>
-  <si>
-    <t>0.3667,0.1487,0.5723,0.0064</t>
-  </si>
-  <si>
-    <t>0.6011,0.5814,0.0058,0.0008</t>
-  </si>
-  <si>
-    <t>0.3821,0.7586,0.0060,0.0004</t>
-  </si>
-  <si>
-    <t>0.9584,0.0741,0.0030,0.0003</t>
-  </si>
-  <si>
-    <t>0.9507,0.0666,0.0029,0.0007</t>
-  </si>
-  <si>
-    <t>0.7674,0.4079,0.0029,0.0005</t>
-  </si>
-  <si>
-    <t>0.3866,0.4618,0.1358,0.0219</t>
-  </si>
-  <si>
-    <t>0.8760,0.0037,0.2281,0.0021</t>
-  </si>
-  <si>
-    <t>0.7519,0.0175,0.2010,0.0433</t>
-  </si>
-  <si>
-    <t>0.8302,0.0089,0.2067,0.0079</t>
-  </si>
-  <si>
-    <t>0.8330,0.0257,0.1736,0.0048</t>
-  </si>
-  <si>
-    <t>0.0051,0.0118,0.9636,0.0287</t>
-  </si>
-  <si>
-    <t>0.0237,0.0797,0.9050,0.0155</t>
-  </si>
-  <si>
-    <t>0.0220,0.0256,0.9563,0.0077</t>
-  </si>
-  <si>
-    <t>0.1151,0.0724,0.8611,0.0016</t>
-  </si>
-  <si>
-    <t>0.1642,0.0243,0.8710,0.0007</t>
-  </si>
-  <si>
-    <t>0.9901,0.0076,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9901,0.0103,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.9932,0.0032,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9036,0.2039,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.9871,0.0134,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.9806,0.0284,0.0008,0.0007</t>
-  </si>
-  <si>
-    <t>0.9909,0.0007,0.0000,0.0049</t>
-  </si>
-  <si>
-    <t>0.9880,0.0062,0.0013,0.0024</t>
-  </si>
-  <si>
-    <t>0.2075,0.0934,0.8620,0.0026</t>
-  </si>
-  <si>
-    <t>0.2062,0.4399,0.3453,0.0029</t>
-  </si>
-  <si>
-    <t>0.9358,0.0164,0.0325,0.0091</t>
-  </si>
-  <si>
-    <t>0.0408,0.0300,0.9610,0.0004</t>
-  </si>
-  <si>
-    <t>0.0014,0.0011,0.9924,0.0181</t>
-  </si>
-  <si>
-    <t>0.0237,0.1087,0.9418,0.0012</t>
-  </si>
-  <si>
-    <t>0.0005,0.0032,0.9972,0.0020</t>
-  </si>
-  <si>
-    <t>0.0638,0.0688,0.8578,0.0016</t>
-  </si>
-  <si>
-    <t>0.0049,0.0130,0.9930,0.0005</t>
-  </si>
-  <si>
-    <t>0.0129,0.0099,0.9781,0.0003</t>
-  </si>
-  <si>
-    <t>0.0417,0.0441,0.9158,0.0040</t>
-  </si>
-  <si>
-    <t>0.5672,0.0489,0.4785,0.0123</t>
-  </si>
-  <si>
-    <t>0.6859,0.0118,0.5024,0.0033</t>
-  </si>
-  <si>
-    <t>0.8053,0.0123,0.1505,0.0281</t>
-  </si>
-  <si>
-    <t>0.9896,0.0170,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9899,0.0118,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9965,0.0027,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9868,0.0158,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9789,0.0111,0.0022,0.0027</t>
-  </si>
-  <si>
-    <t>0.9777,0.0326,0.0029,0.0002</t>
-  </si>
-  <si>
-    <t>0.9918,0.0083,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.9918,0.0057,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.0295,0.0665,0.8689,0.0022</t>
-  </si>
-  <si>
-    <t>0.0013,0.0208,0.9919,0.0010</t>
-  </si>
-  <si>
-    <t>0.0159,0.0280,0.9731,0.0012</t>
-  </si>
-  <si>
-    <t>0.0911,0.0220,0.9122,0.0029</t>
-  </si>
-  <si>
-    <t>0.0508,0.0090,0.9503,0.0041</t>
-  </si>
-  <si>
-    <t>0.2179,0.0255,0.7739,0.0366</t>
-  </si>
-  <si>
-    <t>0.0773,0.0123,0.9158,0.0080</t>
-  </si>
-  <si>
-    <t>0.1873,0.0959,0.6224,0.1995</t>
-  </si>
-  <si>
-    <t>0.3130,0.0004,0.0108,0.7010</t>
-  </si>
-  <si>
-    <t>0.0223,0.0505,0.0025,0.9823</t>
-  </si>
-  <si>
-    <t>0.0627,0.0012,0.0037,0.9677</t>
-  </si>
-  <si>
-    <t>0.0028,0.0002,0.0013,0.9969</t>
-  </si>
-  <si>
-    <t>0.0061,0.0006,0.0007,0.9948</t>
-  </si>
-  <si>
-    <t>0.3353,0.0289,0.0194,0.7090</t>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.7821,0.0193,0.0534,0.1158</t>
+  </si>
+  <si>
+    <t>0.0440,0.0037,0.0035,0.9757</t>
+  </si>
+  <si>
+    <t>0.5181,0.0234,0.0049,0.5575</t>
+  </si>
+  <si>
+    <t>0.1708,0.0047,0.0131,0.8967</t>
+  </si>
+  <si>
+    <t>0.9959,0.0030,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9756,0.0420,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.9741,0.0254,0.0076,0.0021</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9802,0.0122,0.0014,0.0029</t>
+  </si>
+  <si>
+    <t>0.9894,0.0149,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9980,0.0006,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9958,0.0022,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.6568,0.0622,0.3289,0.0052</t>
+  </si>
+  <si>
+    <t>0.0092,0.0228,0.9819,0.0013</t>
+  </si>
+  <si>
+    <t>0.0815,0.0124,0.9486,0.0009</t>
+  </si>
+  <si>
+    <t>0.0091,0.0333,0.9675,0.0019</t>
+  </si>
+  <si>
+    <t>0.4992,0.2830,0.2188,0.0163</t>
+  </si>
+  <si>
+    <t>0.0220,0.9820,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.0175,0.9803,0.0036,0.0002</t>
+  </si>
+  <si>
+    <t>0.2383,0.8483,0.0082,0.0007</t>
+  </si>
+  <si>
+    <t>0.0160,0.9846,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.0143,0.9863,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.5949,0.0249,0.4440,0.0099</t>
+  </si>
+  <si>
+    <t>0.7219,0.0128,0.2242,0.0450</t>
+  </si>
+  <si>
+    <t>0.0253,0.0071,0.9719,0.0017</t>
+  </si>
+  <si>
+    <t>0.0395,0.0095,0.9517,0.0067</t>
+  </si>
+  <si>
+    <t>0.0115,0.0271,0.9662,0.0062</t>
+  </si>
+  <si>
+    <t>0.0567,0.0101,0.9494,0.0016</t>
+  </si>
+  <si>
+    <t>0.0017,0.0017,0.9908,0.0245</t>
+  </si>
+  <si>
+    <t>0.2652,0.7846,0.0080,0.0018</t>
+  </si>
+  <si>
+    <t>0.3894,0.3874,0.1852,0.0008</t>
+  </si>
+  <si>
+    <t>0.0030,0.0258,0.9906,0.0022</t>
+  </si>
+  <si>
+    <t>0.0165,0.8496,0.2154,0.0001</t>
+  </si>
+  <si>
+    <t>0.8874,0.0766,0.0147,0.0181</t>
+  </si>
+  <si>
+    <t>0.9306,0.0768,0.0024,0.0036</t>
+  </si>
+  <si>
+    <t>0.7770,0.4193,0.0018,0.0002</t>
+  </si>
+  <si>
+    <t>0.0675,0.8955,0.1286,0.0056</t>
+  </si>
+  <si>
+    <t>0.0168,0.7967,0.4880,0.0172</t>
+  </si>
+  <si>
+    <t>0.0268,0.0164,0.9737,0.0043</t>
+  </si>
+  <si>
+    <t>0.0336,0.1513,0.9307,0.0007</t>
+  </si>
+  <si>
+    <t>0.0961,0.0495,0.8748,0.0058</t>
+  </si>
+  <si>
+    <t>0.0366,0.3568,0.8240,0.0019</t>
+  </si>
+  <si>
+    <t>0.0053,0.9722,0.1003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0421,0.0694,0.9149,0.0021</t>
+  </si>
+  <si>
+    <t>0.2377,0.1267,0.0049,0.7564</t>
+  </si>
+  <si>
+    <t>0.0035,0.9859,0.0097,0.0044</t>
+  </si>
+  <si>
+    <t>0.0049,0.9869,0.0171,0.0002</t>
+  </si>
+  <si>
+    <t>0.0022,0.9912,0.0352,0.0013</t>
+  </si>
+  <si>
+    <t>0.0448,0.1791,0.8873,0.0040</t>
+  </si>
+  <si>
+    <t>0.0035,0.3327,0.9687,0.0005</t>
+  </si>
+  <si>
+    <t>0.0285,0.0024,0.9589,0.0084</t>
+  </si>
+  <si>
+    <t>0.0408,0.0082,0.9663,0.0016</t>
+  </si>
+  <si>
+    <t>0.0075,0.0193,0.9710,0.0005</t>
+  </si>
+  <si>
+    <t>0.0502,0.0915,0.9210,0.0011</t>
+  </si>
+  <si>
+    <t>0.9804,0.0328,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9856,0.0041,0.0077,0.0007</t>
+  </si>
+  <si>
+    <t>0.9920,0.0040,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.0116,0.0946,0.9812,0.0003</t>
+  </si>
+  <si>
+    <t>0.9951,0.0022,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9941,0.0065,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9790,0.0287,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.0050,0.9410,0.6083,0.0004</t>
+  </si>
+  <si>
+    <t>0.0423,0.0231,0.9281,0.0066</t>
+  </si>
+  <si>
+    <t>0.0493,0.1037,0.8923,0.0099</t>
+  </si>
+  <si>
+    <t>0.0017,0.8418,0.8395,0.0000</t>
+  </si>
+  <si>
+    <t>0.0103,0.0089,0.9883,0.0004</t>
+  </si>
+  <si>
+    <t>0.0172,0.9295,0.1115,0.0005</t>
+  </si>
+  <si>
+    <t>0.0609,0.9264,0.0055,0.0002</t>
+  </si>
+  <si>
+    <t>0.6591,0.0275,0.5266,0.0011</t>
+  </si>
+  <si>
+    <t>0.2070,0.1403,0.7473,0.0038</t>
+  </si>
+  <si>
+    <t>0.0190,0.0163,0.9679,0.0010</t>
+  </si>
+  <si>
+    <t>0.0010,0.7228,0.9533,0.0001</t>
+  </si>
+  <si>
+    <t>0.0037,0.8347,0.8190,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.9853,0.3470,0.0004</t>
+  </si>
+  <si>
+    <t>0.0026,0.9748,0.2737,0.0006</t>
+  </si>
+  <si>
+    <t>0.0395,0.0004,0.0145,0.9479</t>
+  </si>
+  <si>
+    <t>0.0061,0.0023,0.0002,0.9967</t>
+  </si>
+  <si>
+    <t>0.0204,0.0351,0.0011,0.9853</t>
+  </si>
+  <si>
+    <t>0.0500,0.0006,0.0036,0.9663</t>
+  </si>
+  <si>
+    <t>0.0573,0.0025,0.0029,0.9749</t>
+  </si>
+  <si>
+    <t>0.0081,0.0152,0.0003,0.9948</t>
+  </si>
+  <si>
+    <t>0.0011,0.9454,0.6924,0.0001</t>
+  </si>
+  <si>
+    <t>0.0087,0.5832,0.8877,0.0005</t>
+  </si>
+  <si>
+    <t>0.0066,0.9656,0.1313,0.0014</t>
+  </si>
+  <si>
+    <t>0.0018,0.8666,0.9053,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.9954,0.2602,0.0000</t>
+  </si>
+  <si>
+    <t>0.0030,0.9566,0.4155,0.0005</t>
+  </si>
+  <si>
+    <t>0.9840,0.0289,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9706,0.0486,0.0024,0.0003</t>
+  </si>
+  <si>
+    <t>0.9089,0.2174,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.9872,0.0144,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9895,0.0041,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9954,0.0051,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9930,0.0055,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9460,0.0676,0.0085,0.0003</t>
+  </si>
+  <si>
+    <t>0.9950,0.0023,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9866,0.0196,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9967,0.0021,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9977,0.0007,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9936,0.0028,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9978,0.0021,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9961,0.0027,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9979,0.0003,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.0020,0.0017,0.9952,0.0022</t>
+  </si>
+  <si>
+    <t>0.0158,0.0828,0.9555,0.0011</t>
+  </si>
+  <si>
+    <t>0.5428,0.0317,0.4597,0.0257</t>
+  </si>
+  <si>
+    <t>0.0081,0.0071,0.9865,0.0007</t>
+  </si>
+  <si>
+    <t>0.0261,0.9794,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.0688,0.9494,0.0058,0.0007</t>
+  </si>
+  <si>
+    <t>0.1216,0.9308,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.7317,0.4110,0.0035,0.0011</t>
+  </si>
+  <si>
+    <t>0.0222,0.9819,0.0016,0.0004</t>
+  </si>
+  <si>
+    <t>0.0258,0.9782,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.5099,0.6284,0.0047,0.0007</t>
+  </si>
+  <si>
+    <t>0.4018,0.2626,0.3506,0.0104</t>
+  </si>
+  <si>
+    <t>0.2950,0.0105,0.7743,0.0186</t>
+  </si>
+  <si>
+    <t>0.5255,0.2579,0.2040,0.0127</t>
+  </si>
+  <si>
+    <t>0.5799,0.2903,0.1031,0.0080</t>
+  </si>
+  <si>
+    <t>0.0596,0.0476,0.0546,0.9249</t>
+  </si>
+  <si>
+    <t>0.0029,0.9900,0.0098,0.0020</t>
+  </si>
+  <si>
+    <t>0.0007,0.9928,0.0120,0.0075</t>
+  </si>
+  <si>
+    <t>0.0143,0.9650,0.0047,0.0314</t>
+  </si>
+  <si>
+    <t>0.0008,0.9962,0.0327,0.0002</t>
+  </si>
+  <si>
+    <t>0.0178,0.9763,0.0067,0.0014</t>
+  </si>
+  <si>
+    <t>0.8761,0.1516,0.0191,0.0007</t>
+  </si>
+  <si>
+    <t>0.5828,0.5628,0.0062,0.0024</t>
+  </si>
+  <si>
+    <t>0.9758,0.0272,0.0044,0.0005</t>
+  </si>
+  <si>
+    <t>0.9841,0.0130,0.0013,0.0004</t>
+  </si>
+  <si>
+    <t>0.9914,0.0038,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.9523,0.0325,0.0075,0.0034</t>
+  </si>
+  <si>
+    <t>0.9911,0.0037,0.0012,0.0008</t>
+  </si>
+  <si>
+    <t>0.9604,0.0384,0.0090,0.0017</t>
+  </si>
+  <si>
+    <t>0.9706,0.0194,0.0069,0.0044</t>
+  </si>
+  <si>
+    <t>0.9921,0.0066,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.0016,0.7641,0.9438,0.0001</t>
+  </si>
+  <si>
+    <t>0.0101,0.5086,0.8443,0.0007</t>
+  </si>
+  <si>
+    <t>0.0124,0.2737,0.9127,0.0005</t>
+  </si>
+  <si>
+    <t>0.0581,0.0742,0.8635,0.0036</t>
+  </si>
+  <si>
+    <t>0.8452,0.0519,0.0472,0.0029</t>
+  </si>
+  <si>
+    <t>0.5157,0.0096,0.7152,0.0016</t>
+  </si>
+  <si>
+    <t>0.4844,0.0194,0.6977,0.0021</t>
+  </si>
+  <si>
+    <t>0.5207,0.1711,0.2860,0.0203</t>
+  </si>
+  <si>
+    <t>0.0331,0.0007,0.0030,0.9780</t>
+  </si>
+  <si>
+    <t>0.0009,0.0032,0.0027,0.9968</t>
+  </si>
+  <si>
+    <t>0.0298,0.0037,0.0016,0.9810</t>
+  </si>
+  <si>
+    <t>0.0244,0.0009,0.0013,0.9880</t>
+  </si>
+  <si>
+    <t>0.0016,0.7342,0.9549,0.0011</t>
+  </si>
+  <si>
+    <t>0.9259,0.1122,0.0047,0.0007</t>
+  </si>
+  <si>
+    <t>0.2300,0.8377,0.0059,0.0008</t>
+  </si>
+  <si>
+    <t>0.9755,0.0199,0.0044,0.0012</t>
+  </si>
+  <si>
+    <t>0.7392,0.3901,0.0135,0.0010</t>
+  </si>
+  <si>
+    <t>0.9858,0.0042,0.0057,0.0009</t>
+  </si>
+  <si>
+    <t>0.7529,0.0048,0.0068,0.2732</t>
+  </si>
+  <si>
+    <t>0.9588,0.0364,0.0031,0.0020</t>
+  </si>
+  <si>
+    <t>0.0409,0.1990,0.8484,0.0427</t>
+  </si>
+  <si>
+    <t>0.9023,0.0011,0.0071,0.0720</t>
+  </si>
+  <si>
+    <t>0.8588,0.0046,0.0369,0.0723</t>
+  </si>
+  <si>
+    <t>0.2516,0.7513,0.0635,0.0265</t>
+  </si>
+  <si>
+    <t>0.8451,0.1648,0.0146,0.0007</t>
+  </si>
+  <si>
+    <t>0.8904,0.0852,0.0193,0.0035</t>
+  </si>
+  <si>
+    <t>0.3271,0.7005,0.0509,0.0050</t>
+  </si>
+  <si>
+    <t>0.6556,0.3594,0.0434,0.0048</t>
+  </si>
+  <si>
+    <t>0.2301,0.8048,0.0150,0.0062</t>
+  </si>
+  <si>
+    <t>0.9932,0.0045,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9954,0.0013,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9935,0.0013,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9899,0.0016,0.0009,0.0031</t>
+  </si>
+  <si>
+    <t>0.9920,0.0084,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9795,0.0152,0.0007,0.0012</t>
+  </si>
+  <si>
+    <t>0.9935,0.0023,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9977,0.0002,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.7396,0.4433,0.0040,0.0007</t>
+  </si>
+  <si>
+    <t>0.3045,0.7704,0.0081,0.0003</t>
+  </si>
+  <si>
+    <t>0.3515,0.7554,0.0066,0.0002</t>
+  </si>
+  <si>
+    <t>0.2287,0.5623,0.4175,0.0018</t>
+  </si>
+  <si>
+    <t>0.9459,0.0917,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.8927,0.1801,0.0039,0.0008</t>
+  </si>
+  <si>
+    <t>0.9707,0.0321,0.0030,0.0008</t>
+  </si>
+  <si>
+    <t>0.9145,0.1126,0.0060,0.0012</t>
+  </si>
+  <si>
+    <t>0.0017,0.0203,0.9970,0.0001</t>
+  </si>
+  <si>
+    <t>0.9667,0.0285,0.0072,0.0010</t>
+  </si>
+  <si>
+    <t>0.0137,0.0074,0.9861,0.0006</t>
+  </si>
+  <si>
+    <t>0.0006,0.1451,0.9891,0.0003</t>
+  </si>
+  <si>
+    <t>0.0802,0.0185,0.9249,0.0030</t>
+  </si>
+  <si>
+    <t>0.0147,0.0627,0.9703,0.0009</t>
+  </si>
+  <si>
+    <t>0.0018,0.0122,0.9944,0.0002</t>
+  </si>
+  <si>
+    <t>0.0139,0.0036,0.9889,0.0006</t>
+  </si>
+  <si>
+    <t>0.0034,0.0063,0.9925,0.0003</t>
+  </si>
+  <si>
+    <t>0.3750,0.0264,0.7208,0.0039</t>
+  </si>
+  <si>
+    <t>0.0402,0.0121,0.9642,0.0009</t>
+  </si>
+  <si>
+    <t>0.2826,0.2433,0.5040,0.0097</t>
+  </si>
+  <si>
+    <t>0.2117,0.1459,0.6673,0.0035</t>
+  </si>
+  <si>
+    <t>0.4733,0.0637,0.4917,0.0028</t>
+  </si>
+  <si>
+    <t>0.4313,0.0535,0.5505,0.0042</t>
+  </si>
+  <si>
+    <t>0.7124,0.0231,0.3669,0.0084</t>
+  </si>
+  <si>
+    <t>0.4005,0.0403,0.6524,0.0196</t>
+  </si>
+  <si>
+    <t>0.4488,0.7528,0.0022,0.0003</t>
+  </si>
+  <si>
+    <t>0.7351,0.4644,0.0029,0.0003</t>
+  </si>
+  <si>
+    <t>0.5212,0.6480,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.9077,0.1584,0.0043,0.0003</t>
+  </si>
+  <si>
+    <t>0.8934,0.2166,0.0025,0.0003</t>
+  </si>
+  <si>
+    <t>0.5289,0.0576,0.5165,0.0153</t>
+  </si>
+  <si>
+    <t>0.8723,0.0020,0.1788,0.0044</t>
+  </si>
+  <si>
+    <t>0.6803,0.0075,0.2267,0.0648</t>
+  </si>
+  <si>
+    <t>0.1719,0.0299,0.8457,0.0030</t>
+  </si>
+  <si>
+    <t>0.7164,0.0085,0.4572,0.0076</t>
+  </si>
+  <si>
+    <t>0.0014,0.0047,0.9910,0.0071</t>
+  </si>
+  <si>
+    <t>0.0209,0.4151,0.8508,0.0165</t>
+  </si>
+  <si>
+    <t>0.0399,0.0486,0.8568,0.0733</t>
+  </si>
+  <si>
+    <t>0.0829,0.1726,0.8310,0.0010</t>
+  </si>
+  <si>
+    <t>0.0193,0.1044,0.9552,0.0012</t>
+  </si>
+  <si>
+    <t>0.9868,0.0071,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.9938,0.0057,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9837,0.0173,0.0025,0.0007</t>
+  </si>
+  <si>
+    <t>0.9901,0.0094,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9899,0.0112,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9908,0.0081,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9906,0.0083,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9847,0.0205,0.0026,0.0006</t>
+  </si>
+  <si>
+    <t>0.1418,0.0529,0.9000,0.0027</t>
+  </si>
+  <si>
+    <t>0.2715,0.5577,0.2694,0.0047</t>
+  </si>
+  <si>
+    <t>0.9486,0.0304,0.0031,0.0093</t>
+  </si>
+  <si>
+    <t>0.0093,0.0952,0.9655,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,0.9990,0.0010</t>
+  </si>
+  <si>
+    <t>0.0213,0.1017,0.9257,0.0033</t>
+  </si>
+  <si>
+    <t>0.0018,0.0013,0.9969,0.0013</t>
+  </si>
+  <si>
+    <t>0.0583,0.0448,0.8841,0.0104</t>
+  </si>
+  <si>
+    <t>0.0082,0.0016,0.9942,0.0006</t>
+  </si>
+  <si>
+    <t>0.0810,0.0524,0.8782,0.0013</t>
+  </si>
+  <si>
+    <t>0.0243,0.1588,0.9251,0.0033</t>
+  </si>
+  <si>
+    <t>0.7470,0.0069,0.3771,0.0037</t>
+  </si>
+  <si>
+    <t>0.5518,0.0141,0.6297,0.0031</t>
+  </si>
+  <si>
+    <t>0.7892,0.0062,0.2948,0.0082</t>
+  </si>
+  <si>
+    <t>0.9932,0.0052,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9878,0.0100,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9966,0.0035,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9889,0.0080,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.9966,0.0015,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9967,0.0031,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9909,0.0066,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9870,0.0110,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.0566,0.0227,0.9282,0.0012</t>
+  </si>
+  <si>
+    <t>0.0014,0.0267,0.9901,0.0024</t>
+  </si>
+  <si>
+    <t>0.0468,0.0495,0.9317,0.0009</t>
+  </si>
+  <si>
+    <t>0.1634,0.0200,0.8753,0.0007</t>
+  </si>
+  <si>
+    <t>0.0053,0.0025,0.9907,0.0023</t>
+  </si>
+  <si>
+    <t>0.2978,0.0120,0.7656,0.0190</t>
+  </si>
+  <si>
+    <t>0.6227,0.0116,0.3528,0.0468</t>
+  </si>
+  <si>
+    <t>0.0077,0.0360,0.9429,0.0417</t>
+  </si>
+  <si>
+    <t>0.7800,0.0021,0.0241,0.1679</t>
+  </si>
+  <si>
+    <t>0.0160,0.0149,0.0004,0.9909</t>
+  </si>
+  <si>
+    <t>0.1142,0.0038,0.0037,0.9480</t>
+  </si>
+  <si>
+    <t>0.0022,0.0003,0.0015,0.9968</t>
+  </si>
+  <si>
+    <t>0.0169,0.0002,0.0005,0.9909</t>
+  </si>
+  <si>
+    <t>0.3751,0.4520,0.0247,0.1998</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1993,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,10 +2189,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2276,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2290,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2374,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,10 +2413,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2444,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2458,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,10 +2917,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2931,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,10 +2987,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3004,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3130,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,10 +3141,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3158,7 @@
         <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3169,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,10 +3505,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,10 +3561,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3592,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3676,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,10 +3701,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3715,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3858,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,10 +3911,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4040,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4096,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4166,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,10 +4233,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4359,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4376,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4387,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4628,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4670,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4684,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4698,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4712,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,10 +4723,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,10 +4737,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,10 +4779,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5412,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,10 +5423,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,10 +5451,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5521,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
